--- a/data/trans_orig/IP16_n_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>52,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15612</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>20463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23967</t>
+          <t>24176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>38198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52508</t>
+          <t>52299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>32967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13762</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>51728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62770</t>
+          <t>62957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85624</t>
+          <t>85309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110210</t>
+          <t>109750</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>58006</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>74622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72527</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>91336</t>
+          <t>91088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>134820</t>
+          <t>135280</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>159406</t>
+          <t>159721</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26149</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33071</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22256</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>34768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43860</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46469</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55792</t>
+          <t>55748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85296</t>
+          <t>85502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97618</t>
+          <t>97549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18376</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39842</t>
+          <t>39794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36559</t>
+          <t>35835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56177</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107308</t>
+          <t>107051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122123</t>
+          <t>122295</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118766</t>
+          <t>116953</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132974</t>
+          <t>132950</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230747</t>
+          <t>230699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250365</t>
+          <t>251089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>29787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37082</t>
+          <t>37089</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43962</t>
+          <t>44028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>67408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>76569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>25855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47656</t>
+          <t>47780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38609</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101313</t>
+          <t>101824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112351</t>
+          <t>113303</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95520</t>
+          <t>95644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107052</t>
+          <t>107381</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201246</t>
+          <t>201395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217472</t>
+          <t>217520</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36265</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>21927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49514</t>
+          <t>47354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>50196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70866</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28640</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82711</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112447</t>
+          <t>114647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28494</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49133</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,38%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31406</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65916</t>
+          <t>65217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50680</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72167</t>
+          <t>73775</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85890</t>
+          <t>84347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131012</t>
+          <t>130247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109471</t>
+          <t>110170</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143981</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107142</t>
+          <t>105534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128629</t>
+          <t>128803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>223685</t>
+          <t>224450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>268807</t>
+          <t>270350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
